--- a/output/pdf_financials_xlsx/IAI.xlsx
+++ b/output/pdf_financials_xlsx/IAI.xlsx
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.08287700000000001</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.09911300000000001</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.09444900000000001</v>
       </c>
     </row>
     <row r="92">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.439506</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.468313</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.839325</v>
       </c>
     </row>
     <row r="93">
@@ -3206,7 +3206,11 @@
           <t>Reserves (notes 9 and 13)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>4.439506</v>
       </c>
@@ -3260,7 +3264,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.08287700000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/IAI.xlsx
+++ b/output/pdf_financials_xlsx/IAI.xlsx
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.474342</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.326692</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.141295</v>
       </c>
     </row>
     <row r="35">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.474342</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.326692</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.141295</v>
       </c>
     </row>
     <row r="37">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.476691</v>
+        <v>0.002349</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.329086</v>
+        <v>0.002394</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.16098</v>
+        <v>0.019685</v>
       </c>
     </row>
     <row r="49">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/IAI.xlsx
+++ b/output/pdf_financials_xlsx/IAI.xlsx
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.421528</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.5232059999999999</v>
       </c>
     </row>
     <row r="38">
@@ -4624,7 +4624,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
